--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/publication/D5_publication_audit_tables.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/publication/D5_publication_audit_tables.xlsx
@@ -15,10 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monthly_coverage" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="support_sensitivity" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d4_d5_dependence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d4_d5_composite" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="target_influence" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coverage_summary" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coverage_strata" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d4_d5_stratified_rho" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d4_d5_composite" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dimension_availability" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="target_influence" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coverage_summary" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coverage_strata" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,24 +478,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D4_D5_incremental_information</t>
+          <t>D4_D5_dual_scope_overlap</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>accepted_executed_provisional</t>
+          <t>accepted_executed_stale_dependency</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Executed against D4V14_20260726_100717; rerun after the latest D4 release is merged.</t>
+          <t>Report-score and raw-calculable overlap are implemented with analyte/regime/month/pair strata; formal freezing is blocked because dependency status is stale_dependency_blocked.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>score_support_missingness_freeze</t>
+          <t>D4_dependency_fail_closed</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -503,14 +505,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Continuous scores retained; L1/L2/L3 and missing/OOD semantics frozen; A-E grades disabled.</t>
+          <t>Current status requires exact run ID, calibration ID and D4 main-score SHA-256 with one unique run and calibration.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Top1_0_80_boundary</t>
+          <t>score_support_missingness_freeze</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -520,158 +522,209 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Localization failure blocks sensor-specific hard Veto only, not the continuous scientific score.</t>
+          <t>Continuous scores retained; L1/L2/L3 and missing/OOD semantics frozen; A-E grades disabled.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>risk_coverage_and_monthly_support</t>
+          <t>controlled_perturbation_Top1_0_80_boundary</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>accepted_executed_with_limitation</t>
+          <t>accepted_executed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Field evidence coverage and controlled-injection risk-coverage are separate; current confidence is not calibrated for selective localization.</t>
+          <t>Controlled perturbation localization below 0.80 blocks sensor-specific hard Veto only, not the continuous scientific score.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>target_excluded_context</t>
+          <t>risk_coverage_and_monthly_support</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>accepted_with_modification</t>
+          <t>accepted_executed_with_limitation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Production is accurately named plant-global robust context; leave-one-target-out is an influence challenge, not a false production claim.</t>
+          <t>Field evidence coverage and controlled-injection risk-coverage are separate; current confidence is not calibrated for selective localization.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>support_threshold_sensitivity</t>
+          <t>dimension_availability_sensitivity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>accepted_executed</t>
+          <t>accepted_executed_prototype</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sensitivity only; no post-hoc production threshold changes.</t>
+          <t>Availability-aware and fixed-dimension complete-evidence composites are reported separately; rerun after the final D1-D5 numeric contract is frozen.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>untouched_future_test</t>
+          <t>publication_ci</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending_external_data</t>
+          <t>accepted_executed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No untouched data after 2026-04-13 are currently available.</t>
+          <t>Tests, artifact hashes, figure QA and exact D4 dependency are checked by one non-mutating publication bundle gate.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>maintenance_event_truth</t>
+          <t>target_excluded_context</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pending_external_data</t>
+          <t>accepted_with_modification</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Needed for fault/event truth and operational deployment claims.</t>
+          <t>Production is accurately named plant-global robust context; leave-one-target-out is an influence challenge, not a false production claim.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dual_approval_and_asset_provenance</t>
+          <t>support_threshold_sensitivity</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pending_deployment_only</t>
+          <t>accepted_executed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Does not block retrospective scientific aggregation under the confirmed ordinal topology.</t>
+          <t>Sensitivity only; no post-hoc production threshold changes.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>topology_perturbation_robustness</t>
+          <t>untouched_future_test</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pending_prespecified_perturbation_set</t>
+          <t>pending_external_data</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Arbitrary edge edits would be post-hoc; execute only after plausible perturbations are frozen.</t>
+          <t>No untouched data after 2026-04-13 are currently available.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORP_covariance_upgrade</t>
+          <t>maintenance_event_truth</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_executed_not_supported</t>
+          <t>pending_external_data</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Current ORP support does not justify replacing the conservative diagonal model; retain as future sensitivity.</t>
+          <t>Needed for fault/event truth and operational deployment claims.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>dual_approval_and_asset_provenance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>pending_deployment_only</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Does not block retrospective scientific aggregation under the confirmed ordinal topology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>topology_perturbation_robustness</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>pending_prespecified_perturbation_set</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Arbitrary edge edits would be post-hoc; execute only after plausible perturbations are frozen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ORP_covariance_upgrade</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>not_executed_not_supported</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Current ORP support does not justify replacing the conservative diagonal model; retain as future sensitivity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>conditional_mutual_information</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>not_primary</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Autocorrelated single-plant CMI is estimator-sensitive; partial rank plus block bootstrap is the primary audit.</t>
         </is>
@@ -688,638 +741,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>target_sensor</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>analyte</t>
+          <t>spearman_vs_full</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>observed_map_disagreement_rate</t>
+          <t>mean_score_change</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>postreference_map_disagreement_rate</t>
+          <t>p90_absolute_change</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>median_normalized_context_delta</t>
+          <t>n_pair_hours</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>p95_normalized_context_delta</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>injected_context_switch_rate</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>injected_ood_rate_change</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>n_challenge_windows</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>production_model_changed</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>interpretation</t>
+          <t>production_weights_changed</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORP_1_1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ORP</t>
-        </is>
+          <t>without_D4</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.6877316900701674</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1311306423611111</v>
+        <v>0.3836960104588269</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.7601417232291683</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3208671096308404</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.9586327480587914</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.004629629629629629</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
-        </is>
+        <v>37975</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORP_1_2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ORP</t>
-        </is>
+          <t>without_D5</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.8959170552103484</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1472710503472222</v>
+        <v>0.1127866392885466</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.3845032163419386</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3208671096308404</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.9586327480587914</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.05787037037037037</v>
-      </c>
-      <c r="I3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ORP_1_3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ORP</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.1689453125</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.3208671096308404</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9586327480587915</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DO_1_1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.03841145833333334</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.4371699366977927</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.611283480971866</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.01273148148148148</v>
-      </c>
-      <c r="I5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DO_1_2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.05124240451388889</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.4371699366977927</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.611283480971866</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.02546296296296295</v>
-      </c>
-      <c r="I6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DO_1_3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.1800401475694444</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.002351026313409892</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.4371699366977927</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.611283480971866</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.05092592592592593</v>
-      </c>
-      <c r="I7" t="n">
-        <v>6</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DO_1_4</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.03236219618055555</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.4371699366977927</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.611283480971866</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>6</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ORP_2_1</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ORP</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.02566189236111111</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.3208881074130294</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.9586579453974184</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.04166666666666666</v>
-      </c>
-      <c r="I9" t="n">
-        <v>6</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ORP_2_2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ORP</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.06944444444444445</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.3208881074130294</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.9586327480587915</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.001157407407407407</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ORP_2_3</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ORP</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.04041883680555555</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.3208881074130295</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.9586327480587915</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.02083333333333333</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>DO_2_1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.04844835069444445</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.4371699366977927</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.611283480971866</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.02430555555555556</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DO_2_2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.03485785590277778</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.4371699366977927</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.611283480971866</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.01388888888888889</v>
-      </c>
-      <c r="I13" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DO_2_3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0.03209092881944445</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.4371699366977927</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1.611283480971866</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DO_2_4</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.02861870659722222</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.4371699366977927</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1.611283480971866</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
-        </is>
+        <v>37975</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1333,143 +831,604 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>indicator</t>
+          <t>scope</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>sensor_hours</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>interpretation</t>
+          <t>availability_aware_coverage</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>complete_evidence_coverage</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>D5_available_rate</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>availability_aware_median</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>availability_aware_p05</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>availability_aware_complete_median</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>fixed_dimension_median</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>descriptive_median_shift_all_minus_fixed</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>complete_case_contract_max_abs_diff</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>mean_effective_dimension_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dimension_1_rate</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dimension_2_rate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dimension_3_rate</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>estimand</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>full_sensor_hours</t>
+          <t>overall</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39606</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>complete D1-D2-D5 evidence subset</t>
+        <v>86016</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.9957682291666666</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.46044921875</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.4609375</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.336303972752209</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.316042734888346</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.198313025639093</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.198313025639093</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.1379909471131153</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.456217447916667</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.004231770833333333</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.5353190104166666</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.46044921875</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>current_node_level_D1_D2_D5_prototype_repeat_after_final_D1_D5_aggregation</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>basic_sensor_hours</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46046</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>two-dimension extension subset</t>
+        <v>10416</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9731182795698925</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.896505376344086</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9005376344086021</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.306746318546902</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.622489600959386</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.293492394965166</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.293492394965166</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.01325392358173616</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.869623655913978</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.02688172043010753</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.07661290322580645</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.896505376344086</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>current_node_level_D1_D2_D5_prototype_repeat_after_final_D1_D5_aggregation</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>basic_OOD_share</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2906658558832472</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>OOD concentration within Basic</t>
+        <v>10080</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8347222222222223</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8347222222222223</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4.192182939361498</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.062366551820195</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.180081052744901</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.180081052744901</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0121018866165965</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.834722222222222</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1652777777777778</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.8347222222222223</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>current_node_level_D1_D2_D5_prototype_repeat_after_final_D1_D5_aggregation</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>full_OOD_share</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>OOD concentration within Full</t>
+        <v>10416</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.123316406989353</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.256186083425419</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.047846224457858</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.047846224457858</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.07547018253149496</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.791666666666667</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>current_node_level_D1_D2_D5_prototype_repeat_after_final_D1_D5_aggregation</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>basic_L1_share</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7482517482517482</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>lowest D5 support concentration within Basic</t>
+        <v>10080</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.4986111111111111</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.4986111111111111</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.429841393539094</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.583333391789263</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.288033964037393</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.288033964037393</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.1418074295017018</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.498611111111111</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5013888888888889</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.4986111111111111</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>current_node_level_D1_D2_D5_prototype_repeat_after_final_D1_D5_aggregation</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>full_L1_share</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>lowest D5 support concentration within Full</t>
+        <v>10416</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7943548387096774</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.7943548387096774</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4.233922730776071</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.414843507162232</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.190390714327069</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.190390714327069</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.04353201644900118</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.794354838709677</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.2056451612903226</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.7943548387096774</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>current_node_level_D1_D2_D5_prototype_repeat_after_final_D1_D5_aggregation</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>months_without_full_coverage</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>temporal coverage limitation</t>
+        <v>10416</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.02956989247311828</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.02956989247311828</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4.479976904570508</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.173729538682474</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.81665943258665</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.81665943258665</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6633174719838584</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.029569892473118</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.9704301075268817</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.02956989247311828</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>current_node_level_D1_D2_D5_prototype_repeat_after_final_D1_D5_aggregation</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>material_overall_balance_metrics</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>D1_total,D2_total,process_floor_occupancy,D3_warn</t>
+        <v>9408</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.474912974799581</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.250753219320319</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>current_node_level_D1_D2_D5_prototype_repeat_after_final_D1_D5_aggregation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10416</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.508554713392636</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.324045728619065</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>current_node_level_D1_D2_D5_prototype_repeat_after_final_D1_D5_aggregation</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4368</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9807692307692307</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.536920004872278</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.342133232431792</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>1.980769230769231</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.01923076923076923</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.9807692307692307</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>current_node_level_D1_D2_D5_prototype_repeat_after_final_D1_D5_aggregation</t>
         </is>
       </c>
     </row>
@@ -1479,6 +1438,802 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>target_sensor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>analyte</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>observed_map_disagreement_rate</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>postreference_map_disagreement_rate</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>median_normalized_context_delta</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>p95_normalized_context_delta</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>injected_context_switch_rate</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>injected_ood_rate_change</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n_challenge_windows</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>production_model_changed</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ORP_1_1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.1311306423611111</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3208970794720213</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9587222869063324</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.004629629629629629</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ORP_1_2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.148193359375</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3208970794720213</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9587222869063324</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.05787037037037037</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ORP_1_3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1695149739583333</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3208970794720213</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9587222869063325</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DO_1_1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.03830295138888889</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.4371699366977927</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.611283480971866</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.01273148148148148</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DO_1_2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.05124240451388889</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.4371699366977927</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.611283480971866</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.02546296296296295</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DO_1_3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1789279513888889</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.00216998191681736</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.4371699366977927</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.611283480971866</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.05092592592592593</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DO_1_4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.032470703125</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.4371699366977927</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.611283480971866</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ORP_2_1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02571614583333333</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.3209180792154591</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9587474865984579</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ORP_2_2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.06947157118055555</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3209180792154591</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9587222869063325</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.001157407407407407</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ORP_2_3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.03851996527777778</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3209180792154592</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9587222869063325</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DO_2_1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.04798719618055555</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.4371699366977927</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.611283480971866</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.02430555555555556</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DO_2_2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.03461371527777778</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4371699366977927</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.611283480971866</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DO_2_3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.03192816840277778</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.4371699366977927</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.611283480971866</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DO_2_4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.02829318576388889</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.4371699366977927</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.611283480971866</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>bounded_target_influence_sensitivity_not_target_excluded_claim</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>indicator</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>full_sensor_hours</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>39606</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>complete D1-D2-D5 evidence subset</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>basic_sensor_hours</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>46046</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>two-dimension extension subset</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>basic_OOD_share</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.2906658558832472</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>OOD concentration within Basic</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>full_OOD_share</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OOD concentration within Full</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>basic_L1_share</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.7482517482517482</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>lowest D5 support concentration within Basic</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>full_L1_share</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>lowest D5 support concentration within Full</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>months_without_full_coverage</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>temporal coverage limitation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>material_overall_balance_metrics</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>D1_total,D2_total,process_floor_occupancy,D3_warn</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8543,36 +9298,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>overlap_scope</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ci95_low</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ci95_high</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_pair_hours</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>n_time_blocks</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>analysis_unit</t>
         </is>
@@ -8581,22 +9346,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Spearman_rho</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>0.1447844203117691</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>0.05864101364003914</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>0.2481575241197819</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>18376</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
         </is>
@@ -8605,38 +9378,54 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Kendall_tau</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>0.09865786831358302</v>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
         <v>18376</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>pair_hour</t>
+      <c r="G3" t="n">
+        <v>23</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>pair_hour_descriptive</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>partial_rank_correlation</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="n">
         <v>0.1358844307968348</v>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
         <v>18376</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>rank_residual_pair_month_regime_adjusted</t>
         </is>
@@ -8645,22 +9434,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>low_score_Jaccard</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>0.2353553220268443</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>0.1659160096373187</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>0.3067607568531292</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>18376</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
         </is>
@@ -8669,20 +9466,176 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>low_score_joint_lift</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" t="n">
         <v>1.216176000730294</v>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
         <v>18376</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>pair_hour</t>
+      <c r="G6" t="n">
+        <v>23</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>pair_hour_descriptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Spearman_rho</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1384181377374037</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.05529201011971745</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2234997467361922</v>
+      </c>
+      <c r="F7" t="n">
+        <v>37987</v>
+      </c>
+      <c r="G7" t="n">
+        <v>37</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kendall_tau</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.09339694266341063</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>37987</v>
+      </c>
+      <c r="G8" t="n">
+        <v>37</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>pair_hour_descriptive</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>partial_rank_correlation</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1401100141131972</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>37987</v>
+      </c>
+      <c r="G9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>rank_residual_pair_month_regime_adjusted</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>low_score_Jaccard</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.3131121120707467</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2537102351377589</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3677112566087144</v>
+      </c>
+      <c r="F10" t="n">
+        <v>37987</v>
+      </c>
+      <c r="G10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>low_score_joint_lift</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1.142665707072681</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>37987</v>
+      </c>
+      <c r="G11" t="n">
+        <v>37</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>pair_hour_descriptive</t>
         </is>
       </c>
     </row>
@@ -8697,83 +9650,1948 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>variant</t>
+          <t>overlap_scope</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>spearman_vs_full</t>
+          <t>stratum_type</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_score_change</t>
+          <t>stratum_value</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>p90_absolute_change</t>
+          <t>spearman_rho</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>ci95_low</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ci95_high</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>n_pair_hours</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>production_weights_changed</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>n_time_blocks</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>status_reason</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>analysis_unit</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>without_D4</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.6877316900701674</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.3836960104588269</v>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>analyte</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7601417232291683</v>
+        <v>0.1648871709266774</v>
       </c>
       <c r="E2" t="n">
-        <v>37975</v>
-      </c>
-      <c r="F2" t="b">
-        <v>0</v>
+        <v>0.02447081947965471</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3135450742565269</v>
+      </c>
+      <c r="G2" t="n">
+        <v>11228</v>
+      </c>
+      <c r="H2" t="n">
+        <v>23</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>without_D5</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.8959170552103484</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.1127866392885466</v>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>analyte</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>0.3845032163419386</v>
+        <v>0.1263995445036044</v>
       </c>
       <c r="E3" t="n">
-        <v>37975</v>
-      </c>
-      <c r="F3" t="b">
-        <v>0</v>
+        <v>-0.01360351484083131</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2615421231913523</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7148</v>
+      </c>
+      <c r="H3" t="n">
+        <v>23</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.513228826754611</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2362053926147847</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5173160799243584</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1043</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1657400678939403</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.03363776161359748</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.300562193074388</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6507</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1742452418183653</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.09241199048872731</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2866986480689279</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6129</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.05414477311593065</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.03133808772954599</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1709850332616494</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4697</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.184785963710277</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.06695340398379235</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3290210775254468</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4452</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.06642735137048236</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.02624940553157378</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.212114224817723</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3885</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1555001530883052</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.04641194495913831</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2345068760554251</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3907</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1406568563778936</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.05774629775781958</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2618012704749982</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2367</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.3650041288334026</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.09715700249340195</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5851337578385559</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3636</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.008782579931353524</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.05787180256159399</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2362053926147847</v>
+      </c>
+      <c r="G13" t="n">
+        <v>129</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PAIR_DO11</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.254709523139854</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.04264086851853467</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.444162069228968</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2753</v>
+      </c>
+      <c r="H14" t="n">
+        <v>23</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PAIR_DO12</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1373139295349436</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.08199013374604791</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3603516325522506</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2825</v>
+      </c>
+      <c r="H15" t="n">
+        <v>23</v>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PAIR_DO13</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.1447694868045275</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.3750686239476251</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.0978059168099614</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2825</v>
+      </c>
+      <c r="H16" t="n">
+        <v>23</v>
+      </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PAIR_DO14</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.2586612710188049</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.04426007925094853</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.468260764427261</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2825</v>
+      </c>
+      <c r="H17" t="n">
+        <v>23</v>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PAIR_ORP11</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1181849870419339</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.1092960312193946</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3431882707025672</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2593</v>
+      </c>
+      <c r="H18" t="n">
+        <v>23</v>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PAIR_ORP12</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.2728216217044547</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.04513496143531474</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4875977109211334</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2417</v>
+      </c>
+      <c r="H19" t="n">
+        <v>23</v>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>D5_report_score</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PAIR_ORP13</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.09219003131807918</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.2639428801196977</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.09110239417663873</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2138</v>
+      </c>
+      <c r="H20" t="n">
+        <v>23</v>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>analyte</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1073101155509427</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.001791366959307334</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.225659239983356</v>
+      </c>
+      <c r="G21" t="n">
+        <v>24103</v>
+      </c>
+      <c r="H21" t="n">
+        <v>37</v>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>analyte</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ORP</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.1841892521803911</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.07742004420279165</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.281744865245054</v>
+      </c>
+      <c r="G22" t="n">
+        <v>13884</v>
+      </c>
+      <c r="H22" t="n">
+        <v>37</v>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.1826717421780263</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.06406448377681202</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.3061443918434869</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15834</v>
+      </c>
+      <c r="H23" t="n">
+        <v>17</v>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.145565227789108</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.01399852844895695</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.2746806958357535</v>
+      </c>
+      <c r="G24" t="n">
+        <v>9390</v>
+      </c>
+      <c r="H24" t="n">
+        <v>13</v>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.1685180916765592</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.07949895761956288</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.2776680993908811</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6562</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.05685486108107315</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.03986906834314594</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.1654020941276133</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6189</v>
+      </c>
+      <c r="H26" t="n">
+        <v>7</v>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>12</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>insufficient_hours_blocks_or_score_variation</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.1746301128847442</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.06026774555830292</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.3143020574276115</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4807</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5</v>
+      </c>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.04839302066996519</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.04202609377788903</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.1848183698633858</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4509</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5</v>
+      </c>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.1569161339565935</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.05096788767684764</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.2206561010077184</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4960</v>
+      </c>
+      <c r="H30" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.1053591576112445</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.06974551297344025</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.2266223765069477</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4782</v>
+      </c>
+      <c r="H31" t="n">
+        <v>5</v>
+      </c>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.4629525145587797</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.09329345966796689</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.6355960240523886</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4612</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5</v>
+      </c>
+      <c r="I32" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.05869916163315617</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.2017337571775558</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.3415260208407785</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4628</v>
+      </c>
+      <c r="H33" t="n">
+        <v>6</v>
+      </c>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.09606238141869745</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.03264083321930808</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.2151694544439619</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3713</v>
+      </c>
+      <c r="H34" t="n">
+        <v>5</v>
+      </c>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.3383504951945573</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.2098416178167383</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.4768416850383361</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4005</v>
+      </c>
+      <c r="H35" t="n">
+        <v>5</v>
+      </c>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.04354408963858887</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.467758799771775</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.4141241955859272</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1971</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PAIR_DO11</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.1661977852485299</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.03295308865950863</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.3589342604749517</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5969</v>
+      </c>
+      <c r="H37" t="n">
+        <v>37</v>
+      </c>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PAIR_DO12</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.03007163084027335</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.1943356407000376</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.2494087771034263</v>
+      </c>
+      <c r="G38" t="n">
+        <v>6044</v>
+      </c>
+      <c r="H38" t="n">
+        <v>37</v>
+      </c>
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PAIR_DO13</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.1676713913448296</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.02551803006772493</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.3459133528337808</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6045</v>
+      </c>
+      <c r="H39" t="n">
+        <v>37</v>
+      </c>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PAIR_DO14</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.0470028544447773</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.1281995582378314</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.2249743563397756</v>
+      </c>
+      <c r="G40" t="n">
+        <v>6045</v>
+      </c>
+      <c r="H40" t="n">
+        <v>37</v>
+      </c>
+      <c r="I40" t="b">
+        <v>1</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PAIR_ORP11</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.1823509955763661</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-0.001652947574804879</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.3620129403030196</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5650</v>
+      </c>
+      <c r="H41" t="n">
+        <v>37</v>
+      </c>
+      <c r="I41" t="b">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PAIR_ORP12</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.5081551132491087</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.3421980427888295</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.6191530351249586</v>
+      </c>
+      <c r="G42" t="n">
+        <v>4303</v>
+      </c>
+      <c r="H42" t="n">
+        <v>37</v>
+      </c>
+      <c r="I42" t="b">
+        <v>1</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>D5_raw_calculable</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PAIR_ORP13</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.100472819525351</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-0.2624264766546522</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.05907050036774079</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3931</v>
+      </c>
+      <c r="H43" t="n">
+        <v>37</v>
+      </c>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>estimable</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>synchronized_7d_time_block</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/publication/D5_publication_audit_tables.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/publication/D5_publication_audit_tables.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>accepted_executed_stale_dependency</t>
+          <t>accepted_executed_current</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Report-score and raw-calculable overlap are implemented with analyte/regime/month/pair strata; formal freezing is blocked because dependency status is stale_dependency_blocked.</t>
+          <t>Report-score and raw-calculable overlap use analyte/regime/month/pair strata with separate descriptive and inferential admission; dependency status is current.</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,6 +775,21 @@
           <t>production_weights_changed</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>source_D4_run_id</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>source_D4_calibration_id</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>source_D4_sha256</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -797,6 +812,21 @@
       <c r="F2" t="b">
         <v>0</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -818,6 +848,21 @@
       </c>
       <c r="F3" t="b">
         <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -9298,7 +9343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9342,6 +9387,21 @@
           <t>analysis_unit</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>source_D4_run_id</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>source_D4_calibration_id</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>source_D4_sha256</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9355,16 +9415,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1447844203117691</v>
+        <v>0.1188315838545302</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05864101364003914</v>
+        <v>0.04710521315174847</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2481575241197819</v>
+        <v>0.1995383959868399</v>
       </c>
       <c r="F2" t="n">
-        <v>18376</v>
+        <v>19774</v>
       </c>
       <c r="G2" t="n">
         <v>23</v>
@@ -9374,6 +9434,21 @@
           <t>synchronized_7d_time_block</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9387,12 +9462,12 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09865786831358302</v>
+        <v>0.08087269655817959</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>18376</v>
+        <v>19774</v>
       </c>
       <c r="G3" t="n">
         <v>23</v>
@@ -9402,6 +9477,21 @@
           <t>pair_hour_descriptive</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9415,12 +9505,12 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1358844307968348</v>
+        <v>0.1084581198320218</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>18376</v>
+        <v>19774</v>
       </c>
       <c r="G4" t="n">
         <v>23</v>
@@ -9430,6 +9520,21 @@
           <t>rank_residual_pair_month_regime_adjusted</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9443,16 +9548,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.2353553220268443</v>
+        <v>0.2293999425782371</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1659160096373187</v>
+        <v>0.166535972040293</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3067607568531292</v>
+        <v>0.2930904213393423</v>
       </c>
       <c r="F5" t="n">
-        <v>18376</v>
+        <v>19774</v>
       </c>
       <c r="G5" t="n">
         <v>23</v>
@@ -9462,6 +9567,21 @@
           <t>synchronized_7d_time_block</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9475,12 +9595,12 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.216176000730294</v>
+        <v>1.187442266664128</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>18376</v>
+        <v>19774</v>
       </c>
       <c r="G6" t="n">
         <v>23</v>
@@ -9490,6 +9610,21 @@
           <t>pair_hour_descriptive</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9503,16 +9638,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1384181377374037</v>
+        <v>0.1709287648135908</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05529201011971745</v>
+        <v>0.08872559112986397</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2234997467361922</v>
+        <v>0.243624764309084</v>
       </c>
       <c r="F7" t="n">
-        <v>37987</v>
+        <v>42371</v>
       </c>
       <c r="G7" t="n">
         <v>37</v>
@@ -9522,6 +9657,21 @@
           <t>synchronized_7d_time_block</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9535,12 +9685,12 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.09339694266341063</v>
+        <v>0.1147791249723404</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>37987</v>
+        <v>42371</v>
       </c>
       <c r="G8" t="n">
         <v>37</v>
@@ -9550,6 +9700,21 @@
           <t>pair_hour_descriptive</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9563,12 +9728,12 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.1401100141131972</v>
+        <v>0.1427654099274315</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>37987</v>
+        <v>42371</v>
       </c>
       <c r="G9" t="n">
         <v>37</v>
@@ -9578,6 +9743,21 @@
           <t>rank_residual_pair_month_regime_adjusted</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9591,16 +9771,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.3131121120707467</v>
+        <v>0.3403883282940512</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2537102351377589</v>
+        <v>0.2752831403224458</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3677112566087144</v>
+        <v>0.3989756986314746</v>
       </c>
       <c r="F10" t="n">
-        <v>37987</v>
+        <v>42371</v>
       </c>
       <c r="G10" t="n">
         <v>37</v>
@@ -9610,6 +9790,21 @@
           <t>synchronized_7d_time_block</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9623,12 +9818,12 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.142665707072681</v>
+        <v>1.173796699884706</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>37987</v>
+        <v>42371</v>
       </c>
       <c r="G11" t="n">
         <v>37</v>
@@ -9636,6 +9831,21 @@
       <c r="H11" t="inlineStr">
         <is>
           <t>pair_hour_descriptive</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9701,12 +9911,37 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>descriptive_estimable</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>status_reason</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>analysis_unit</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>source_D4_run_id</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>source_D4_calibration_id</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>source_D4_sha256</t>
         </is>
       </c>
     </row>
@@ -9727,16 +9962,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1648871709266774</v>
+        <v>0.1598127213982356</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02447081947965471</v>
+        <v>0.02044745877641351</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3135450742565269</v>
+        <v>0.3032622893615987</v>
       </c>
       <c r="G2" t="n">
-        <v>11228</v>
+        <v>11299</v>
       </c>
       <c r="H2" t="n">
         <v>23</v>
@@ -9744,14 +9979,35 @@
       <c r="I2" t="b">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -9772,16 +10028,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1263995445036044</v>
+        <v>0.0797093057588512</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.01360351484083131</v>
+        <v>-0.05114047511035813</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2615421231913523</v>
+        <v>0.2075996729811067</v>
       </c>
       <c r="G3" t="n">
-        <v>7148</v>
+        <v>8475</v>
       </c>
       <c r="H3" t="n">
         <v>23</v>
@@ -9789,14 +10045,35 @@
       <c r="I3" t="b">
         <v>1</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -9817,16 +10094,12 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.513228826754611</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.2362053926147847</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.5173160799243584</v>
-      </c>
+        <v>0.4402850199851668</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>1043</v>
+        <v>1120</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -9834,14 +10107,35 @@
       <c r="I4" t="b">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -9862,16 +10156,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1657400678939403</v>
+        <v>0.08823341372881678</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03363776161359748</v>
+        <v>-0.009280771995007807</v>
       </c>
       <c r="F5" t="n">
-        <v>0.300562193074388</v>
+        <v>0.1764686539828898</v>
       </c>
       <c r="G5" t="n">
-        <v>6507</v>
+        <v>7168</v>
       </c>
       <c r="H5" t="n">
         <v>12</v>
@@ -9879,14 +10173,35 @@
       <c r="I5" t="b">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -9907,16 +10222,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1742452418183653</v>
+        <v>0.1954746506358939</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09241199048872731</v>
+        <v>0.1077290142656085</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2866986480689279</v>
+        <v>0.3203813378595837</v>
       </c>
       <c r="G6" t="n">
-        <v>6129</v>
+        <v>6460</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
@@ -9924,14 +10239,35 @@
       <c r="I6" t="b">
         <v>1</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -9952,16 +10288,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.05414477311593065</v>
+        <v>0.04621402964994677</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.03133808772954599</v>
+        <v>-0.04907784215363829</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1709850332616494</v>
+        <v>0.1687900228078297</v>
       </c>
       <c r="G7" t="n">
-        <v>4697</v>
+        <v>5026</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -9969,14 +10305,35 @@
       <c r="I7" t="b">
         <v>1</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -9997,16 +10354,12 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.184785963710277</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.06695340398379235</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.3290210775254468</v>
-      </c>
+        <v>0.2007104479213656</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>4452</v>
+        <v>4668</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -10014,14 +10367,35 @@
       <c r="I8" t="b">
         <v>1</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10042,16 +10416,12 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.06642735137048236</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-0.02624940553157378</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.212114224817723</v>
-      </c>
+        <v>0.05948948626695483</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>3885</v>
+        <v>4193</v>
       </c>
       <c r="H9" t="n">
         <v>5</v>
@@ -10059,14 +10429,35 @@
       <c r="I9" t="b">
         <v>1</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10087,16 +10478,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1555001530883052</v>
+        <v>0.1500191582519086</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04641194495913831</v>
+        <v>0.03850358759327382</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2345068760554251</v>
+        <v>0.2267186973945168</v>
       </c>
       <c r="G10" t="n">
-        <v>3907</v>
+        <v>4123</v>
       </c>
       <c r="H10" t="n">
         <v>6</v>
@@ -10104,14 +10495,35 @@
       <c r="I10" t="b">
         <v>1</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10132,16 +10544,12 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1406568563778936</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-0.05774629775781958</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.2618012704749982</v>
-      </c>
+        <v>0.1607173768372455</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>2367</v>
+        <v>2513</v>
       </c>
       <c r="H11" t="n">
         <v>5</v>
@@ -10149,14 +10557,35 @@
       <c r="I11" t="b">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10177,16 +10606,12 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.3650041288334026</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.09715700249340195</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.5851337578385559</v>
-      </c>
+        <v>0.1996183204300839</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>3636</v>
+        <v>4137</v>
       </c>
       <c r="H12" t="n">
         <v>5</v>
@@ -10194,14 +10619,35 @@
       <c r="I12" t="b">
         <v>1</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10222,16 +10668,12 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.008782579931353524</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.05787180256159399</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.2362053926147847</v>
-      </c>
+        <v>-0.03715756645859602</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="H13" t="n">
         <v>2</v>
@@ -10239,14 +10681,35 @@
       <c r="I13" t="b">
         <v>1</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10267,16 +10730,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.254709523139854</v>
+        <v>0.24716166757365</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04264086851853467</v>
+        <v>0.02349297625726329</v>
       </c>
       <c r="F14" t="n">
-        <v>0.444162069228968</v>
+        <v>0.4411344102177019</v>
       </c>
       <c r="G14" t="n">
-        <v>2753</v>
+        <v>2824</v>
       </c>
       <c r="H14" t="n">
         <v>23</v>
@@ -10284,14 +10747,35 @@
       <c r="I14" t="b">
         <v>1</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10312,13 +10796,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.1373139295349436</v>
+        <v>0.128732791895169</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.08199013374604791</v>
+        <v>-0.09739145461226639</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3603516325522506</v>
+        <v>0.3397264958015012</v>
       </c>
       <c r="G15" t="n">
         <v>2825</v>
@@ -10329,14 +10813,35 @@
       <c r="I15" t="b">
         <v>1</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10357,13 +10862,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.1447694868045275</v>
+        <v>-0.1447789726746014</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3750686239476251</v>
+        <v>-0.3684639307392786</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0978059168099614</v>
+        <v>0.0987949365805483</v>
       </c>
       <c r="G16" t="n">
         <v>2825</v>
@@ -10374,14 +10879,35 @@
       <c r="I16" t="b">
         <v>1</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10402,13 +10928,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.2586612710188049</v>
+        <v>0.2548884117033289</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04426007925094853</v>
+        <v>0.02977644760351317</v>
       </c>
       <c r="F17" t="n">
-        <v>0.468260764427261</v>
+        <v>0.458571308054424</v>
       </c>
       <c r="G17" t="n">
         <v>2825</v>
@@ -10419,14 +10945,35 @@
       <c r="I17" t="b">
         <v>1</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10447,16 +10994,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.1181849870419339</v>
+        <v>0.1174065870459576</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1092960312193946</v>
+        <v>-0.1057320290409087</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3431882707025672</v>
+        <v>0.3408855475779765</v>
       </c>
       <c r="G18" t="n">
-        <v>2593</v>
+        <v>2825</v>
       </c>
       <c r="H18" t="n">
         <v>23</v>
@@ -10464,14 +11011,35 @@
       <c r="I18" t="b">
         <v>1</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10492,16 +11060,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.2728216217044547</v>
+        <v>0.2326659017374983</v>
       </c>
       <c r="E19" t="n">
-        <v>0.04513496143531474</v>
+        <v>0.01782860933143079</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4875977109211334</v>
+        <v>0.450705114853767</v>
       </c>
       <c r="G19" t="n">
-        <v>2417</v>
+        <v>2825</v>
       </c>
       <c r="H19" t="n">
         <v>23</v>
@@ -10509,14 +11077,35 @@
       <c r="I19" t="b">
         <v>1</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10537,16 +11126,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.09219003131807918</v>
+        <v>-0.1389312561316479</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2639428801196977</v>
+        <v>-0.305483084219249</v>
       </c>
       <c r="F20" t="n">
-        <v>0.09110239417663873</v>
+        <v>0.05240985521479488</v>
       </c>
       <c r="G20" t="n">
-        <v>2138</v>
+        <v>2825</v>
       </c>
       <c r="H20" t="n">
         <v>23</v>
@@ -10554,14 +11143,35 @@
       <c r="I20" t="b">
         <v>1</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10582,16 +11192,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.1073101155509427</v>
+        <v>0.08850978279548977</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.001791366959307334</v>
+        <v>-0.02240861765470454</v>
       </c>
       <c r="F21" t="n">
-        <v>0.225659239983356</v>
+        <v>0.2031283389567795</v>
       </c>
       <c r="G21" t="n">
-        <v>24103</v>
+        <v>24179</v>
       </c>
       <c r="H21" t="n">
         <v>37</v>
@@ -10599,14 +11209,35 @@
       <c r="I21" t="b">
         <v>1</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10627,16 +11258,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.1841892521803911</v>
+        <v>0.249933899818186</v>
       </c>
       <c r="E22" t="n">
-        <v>0.07742004420279165</v>
+        <v>0.1396113269718088</v>
       </c>
       <c r="F22" t="n">
-        <v>0.281744865245054</v>
+        <v>0.3432159250277849</v>
       </c>
       <c r="G22" t="n">
-        <v>13884</v>
+        <v>18192</v>
       </c>
       <c r="H22" t="n">
         <v>37</v>
@@ -10644,14 +11275,35 @@
       <c r="I22" t="b">
         <v>1</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10672,16 +11324,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.1826717421780263</v>
+        <v>0.2608244375254192</v>
       </c>
       <c r="E23" t="n">
-        <v>0.06406448377681202</v>
+        <v>0.135978299732926</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3061443918434869</v>
+        <v>0.3752903022006445</v>
       </c>
       <c r="G23" t="n">
-        <v>15834</v>
+        <v>18614</v>
       </c>
       <c r="H23" t="n">
         <v>17</v>
@@ -10689,14 +11341,35 @@
       <c r="I23" t="b">
         <v>1</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10717,16 +11390,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.145565227789108</v>
+        <v>0.09819348253400323</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01399852844895695</v>
+        <v>-0.01108541438983866</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2746806958357535</v>
+        <v>0.1970378857516808</v>
       </c>
       <c r="G24" t="n">
-        <v>9390</v>
+        <v>10220</v>
       </c>
       <c r="H24" t="n">
         <v>13</v>
@@ -10734,14 +11407,35 @@
       <c r="I24" t="b">
         <v>1</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10762,16 +11456,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1685180916765592</v>
+        <v>0.1910526677041139</v>
       </c>
       <c r="E25" t="n">
-        <v>0.07949895761956288</v>
+        <v>0.09996746995845496</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2776680993908811</v>
+        <v>0.3094360034803626</v>
       </c>
       <c r="G25" t="n">
-        <v>6562</v>
+        <v>6929</v>
       </c>
       <c r="H25" t="n">
         <v>6</v>
@@ -10779,14 +11473,35 @@
       <c r="I25" t="b">
         <v>1</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10807,16 +11522,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.05685486108107315</v>
+        <v>0.04779975957437405</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.03986906834314594</v>
+        <v>-0.05995896924131323</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1654020941276133</v>
+        <v>0.1574734162258497</v>
       </c>
       <c r="G26" t="n">
-        <v>6189</v>
+        <v>6594</v>
       </c>
       <c r="H26" t="n">
         <v>7</v>
@@ -10824,14 +11539,35 @@
       <c r="I26" t="b">
         <v>1</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10855,7 +11591,7 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -10863,14 +11599,35 @@
       <c r="I27" t="b">
         <v>0</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>insufficient_hours_blocks_or_score_variation</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10891,16 +11648,12 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.1746301128847442</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.06026774555830292</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.3143020574276115</v>
-      </c>
+        <v>0.1917876472307921</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>4807</v>
+        <v>5046</v>
       </c>
       <c r="H28" t="n">
         <v>5</v>
@@ -10908,14 +11661,35 @@
       <c r="I28" t="b">
         <v>1</v>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10936,16 +11710,12 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.04839302066996519</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-0.04202609377788903</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.1848183698633858</v>
-      </c>
+        <v>0.04172147146409691</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>4509</v>
+        <v>4879</v>
       </c>
       <c r="H29" t="n">
         <v>5</v>
@@ -10953,14 +11723,35 @@
       <c r="I29" t="b">
         <v>1</v>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -10981,16 +11772,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.1569161339565935</v>
+        <v>0.1497605480172237</v>
       </c>
       <c r="E30" t="n">
-        <v>0.05096788767684764</v>
+        <v>0.03986727305263311</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2206561010077184</v>
+        <v>0.2146163969261723</v>
       </c>
       <c r="G30" t="n">
-        <v>4960</v>
+        <v>5208</v>
       </c>
       <c r="H30" t="n">
         <v>6</v>
@@ -10998,14 +11789,35 @@
       <c r="I30" t="b">
         <v>1</v>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -11026,16 +11838,12 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.1053591576112445</v>
-      </c>
-      <c r="E31" t="n">
-        <v>-0.06974551297344025</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.2266223765069477</v>
-      </c>
+        <v>0.1237122592055719</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>4782</v>
+        <v>5040</v>
       </c>
       <c r="H31" t="n">
         <v>5</v>
@@ -11043,14 +11851,35 @@
       <c r="I31" t="b">
         <v>1</v>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -11071,16 +11900,12 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.4629525145587797</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.09329345966796689</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.6355960240523886</v>
-      </c>
+        <v>0.3257640751239155</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>4612</v>
+        <v>5208</v>
       </c>
       <c r="H32" t="n">
         <v>5</v>
@@ -11088,14 +11913,35 @@
       <c r="I32" t="b">
         <v>1</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -11116,16 +11962,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.05869916163315617</v>
+        <v>0.07138776183439244</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2017337571775558</v>
+        <v>-0.205172509800874</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3415260208407785</v>
+        <v>0.3873738525301996</v>
       </c>
       <c r="G33" t="n">
-        <v>4628</v>
+        <v>4998</v>
       </c>
       <c r="H33" t="n">
         <v>6</v>
@@ -11133,14 +11979,35 @@
       <c r="I33" t="b">
         <v>1</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -11161,16 +12028,12 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.09606238141869745</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-0.03264083321930808</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.2151694544439619</v>
-      </c>
+        <v>0.1257937734771043</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>3713</v>
+        <v>4704</v>
       </c>
       <c r="H34" t="n">
         <v>5</v>
@@ -11178,14 +12041,35 @@
       <c r="I34" t="b">
         <v>1</v>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -11206,16 +12090,12 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.3383504951945573</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.2098416178167383</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.4768416850383361</v>
-      </c>
+        <v>0.3919183763708834</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>4005</v>
+        <v>5132</v>
       </c>
       <c r="H35" t="n">
         <v>5</v>
@@ -11223,14 +12103,35 @@
       <c r="I35" t="b">
         <v>1</v>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -11251,16 +12152,12 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-0.04354408963858887</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.467758799771775</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.4141241955859272</v>
-      </c>
+        <v>0.002616591107560273</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>1971</v>
+        <v>2156</v>
       </c>
       <c r="H36" t="n">
         <v>3</v>
@@ -11268,14 +12165,35 @@
       <c r="I36" t="b">
         <v>1</v>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>descriptive_only_insufficient_independent_blocks_for_ci</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -11296,16 +12214,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.1661977852485299</v>
+        <v>0.153386101794495</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.03295308865950863</v>
+        <v>-0.05747535146914793</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3589342604749517</v>
+        <v>0.3397674720916619</v>
       </c>
       <c r="G37" t="n">
-        <v>5969</v>
+        <v>6044</v>
       </c>
       <c r="H37" t="n">
         <v>37</v>
@@ -11313,14 +12231,35 @@
       <c r="I37" t="b">
         <v>1</v>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -11341,16 +12280,16 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.03007163084027335</v>
+        <v>0.01481212208169198</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.1943356407000376</v>
+        <v>-0.1964467217113791</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2494087771034263</v>
+        <v>0.2379039090324816</v>
       </c>
       <c r="G38" t="n">
-        <v>6044</v>
+        <v>6045</v>
       </c>
       <c r="H38" t="n">
         <v>37</v>
@@ -11358,14 +12297,35 @@
       <c r="I38" t="b">
         <v>1</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
+      <c r="J38" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -11386,13 +12346,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.1676713913448296</v>
+        <v>0.1460952880188521</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.02551803006772493</v>
+        <v>-0.06255067730168695</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3459133528337808</v>
+        <v>0.3106787301503341</v>
       </c>
       <c r="G39" t="n">
         <v>6045</v>
@@ -11403,14 +12363,35 @@
       <c r="I39" t="b">
         <v>1</v>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -11431,13 +12412,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.0470028544447773</v>
+        <v>0.02275386446749715</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.1281995582378314</v>
+        <v>-0.1492998099358729</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2249743563397756</v>
+        <v>0.2215409657159585</v>
       </c>
       <c r="G40" t="n">
         <v>6045</v>
@@ -11448,14 +12429,35 @@
       <c r="I40" t="b">
         <v>1</v>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -11476,16 +12478,16 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.1823509955763661</v>
+        <v>0.1805133147913669</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.001652947574804879</v>
+        <v>-0.007679192376166156</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3620129403030196</v>
+        <v>0.3571454981283404</v>
       </c>
       <c r="G41" t="n">
-        <v>5650</v>
+        <v>6064</v>
       </c>
       <c r="H41" t="n">
         <v>37</v>
@@ -11493,14 +12495,35 @@
       <c r="I41" t="b">
         <v>1</v>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -11521,16 +12544,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.5081551132491087</v>
+        <v>0.5369511811396844</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3421980427888295</v>
+        <v>0.3900795351799278</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6191530351249586</v>
+        <v>0.6241342020362962</v>
       </c>
       <c r="G42" t="n">
-        <v>4303</v>
+        <v>6064</v>
       </c>
       <c r="H42" t="n">
         <v>37</v>
@@ -11538,14 +12561,35 @@
       <c r="I42" t="b">
         <v>1</v>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
+      <c r="J42" t="b">
+        <v>1</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
@@ -11566,16 +12610,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-0.100472819525351</v>
+        <v>0.004864951203155672</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.2624264766546522</v>
+        <v>-0.173404562961704</v>
       </c>
       <c r="F43" t="n">
-        <v>0.05907050036774079</v>
+        <v>0.1753492915771968</v>
       </c>
       <c r="G43" t="n">
-        <v>3931</v>
+        <v>6064</v>
       </c>
       <c r="H43" t="n">
         <v>37</v>
@@ -11583,14 +12627,35 @@
       <c r="I43" t="b">
         <v>1</v>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>estimable</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
+      <c r="J43" t="b">
+        <v>1</v>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>inferential_estimable</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>synchronized_7d_time_block</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>D4V151_20260813_083347</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>D4CAL-V151-66fe1bb6b7d3</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>c21738a331d19632cc915e4d29cf692920aeccd346a6c74912f0f52dd4a9ca04</t>
         </is>
       </c>
     </row>
